--- a/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
@@ -173,7 +173,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-21T18:04:35.562Z</t>
+    <t>2026-05-22T15:27:24.647Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
@@ -173,7 +173,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-22T15:27:24.647Z</t>
+    <t>2026-05-22T15:52:44.832Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
@@ -173,7 +173,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-22T15:52:44.832Z</t>
+    <t>2026-05-24T22:28:17.950Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
@@ -173,7 +173,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-24T22:28:17.950Z</t>
+    <t>2026-05-25T13:08:48.807Z</t>
   </si>
   <si>
     <t>Data Source</t>

--- a/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
+++ b/src/data/downloads/local_2014_2016_oct30_sakrebulo_by_election_20161030_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="60">
   <si>
     <t>district_id</t>
   </si>
@@ -107,6 +107,9 @@
     <t>precinct_number</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>26.15.8</t>
   </si>
   <si>
@@ -173,7 +176,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-05-25T13:08:48.807Z</t>
+    <t>2026-06-13T11:36:45.147Z</t>
   </si>
   <si>
     <t>Data Source</t>
@@ -697,40 +700,40 @@
         <v>243</v>
       </c>
       <c r="F2" s="2">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G2" s="2">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H2" s="2">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I2" s="2">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J2" s="2">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K2" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M2" s="2">
         <v>10.42</v>
       </c>
       <c r="N2" s="2">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O2" s="2">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P2" s="2">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q2" s="2">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -750,40 +753,40 @@
         <v>799</v>
       </c>
       <c r="F3">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G3">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H3">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I3">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J3">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M3">
         <v>34.25</v>
       </c>
       <c r="N3">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O3">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P3">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q3">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -803,40 +806,40 @@
         <v>575</v>
       </c>
       <c r="F4" s="2">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G4" s="2">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H4" s="2">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I4" s="2">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J4" s="2">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K4" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M4" s="2">
         <v>24.65</v>
       </c>
       <c r="N4" s="2">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O4" s="2">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P4" s="2">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q4" s="2">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -856,40 +859,40 @@
         <v>416</v>
       </c>
       <c r="F5">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G5">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H5">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I5">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J5">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K5">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L5">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M5">
         <v>17.83</v>
       </c>
       <c r="N5">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O5">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P5">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q5">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -909,40 +912,40 @@
         <v>300</v>
       </c>
       <c r="F6" s="2">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G6" s="2">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H6" s="2">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I6" s="2">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J6" s="2">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K6" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M6" s="2">
         <v>12.86</v>
       </c>
       <c r="N6" s="2">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O6" s="2">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P6" s="2">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q6" s="2">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -962,40 +965,40 @@
         <v>243</v>
       </c>
       <c r="F7">
-        <v>1887</v>
+        <v>1129</v>
       </c>
       <c r="G7">
-        <v>1015</v>
+        <v>591</v>
       </c>
       <c r="H7">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="I7">
-        <v>824</v>
+        <v>486</v>
       </c>
       <c r="J7">
-        <v>1863</v>
+        <v>1110</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L7">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M7">
         <v>16.67</v>
       </c>
       <c r="N7">
-        <v>53.79</v>
+        <v>52.35</v>
       </c>
       <c r="O7">
-        <v>16.69</v>
+        <v>16.12</v>
       </c>
       <c r="P7">
-        <v>43.67</v>
+        <v>43.05</v>
       </c>
       <c r="Q7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1015,40 +1018,40 @@
         <v>799</v>
       </c>
       <c r="F8" s="2">
-        <v>1887</v>
+        <v>1129</v>
       </c>
       <c r="G8" s="2">
-        <v>1015</v>
+        <v>591</v>
       </c>
       <c r="H8" s="2">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="I8" s="2">
-        <v>824</v>
+        <v>486</v>
       </c>
       <c r="J8" s="2">
-        <v>1863</v>
+        <v>1110</v>
       </c>
       <c r="K8" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M8" s="2">
         <v>54.8</v>
       </c>
       <c r="N8" s="2">
-        <v>53.79</v>
+        <v>52.35</v>
       </c>
       <c r="O8" s="2">
-        <v>16.69</v>
+        <v>16.12</v>
       </c>
       <c r="P8" s="2">
-        <v>43.67</v>
+        <v>43.05</v>
       </c>
       <c r="Q8" s="2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1068,40 +1071,40 @@
         <v>416</v>
       </c>
       <c r="F9">
-        <v>1887</v>
+        <v>1129</v>
       </c>
       <c r="G9">
-        <v>1015</v>
+        <v>591</v>
       </c>
       <c r="H9">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="I9">
-        <v>824</v>
+        <v>486</v>
       </c>
       <c r="J9">
-        <v>1863</v>
+        <v>1110</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L9">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M9">
         <v>28.53</v>
       </c>
       <c r="N9">
-        <v>53.79</v>
+        <v>52.35</v>
       </c>
       <c r="O9">
-        <v>16.69</v>
+        <v>16.12</v>
       </c>
       <c r="P9">
-        <v>43.67</v>
+        <v>43.05</v>
       </c>
       <c r="Q9">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1121,40 +1124,40 @@
         <v>575</v>
       </c>
       <c r="F10" s="2">
-        <v>1938</v>
+        <v>1371</v>
       </c>
       <c r="G10" s="2">
-        <v>918</v>
+        <v>598</v>
       </c>
       <c r="H10" s="2">
-        <v>359</v>
+        <v>236</v>
       </c>
       <c r="I10" s="2">
-        <v>761</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2">
-        <v>1934</v>
+        <v>1370</v>
       </c>
       <c r="K10" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="M10" s="2">
         <v>65.71</v>
       </c>
       <c r="N10" s="2">
-        <v>47.37</v>
+        <v>43.62</v>
       </c>
       <c r="O10" s="2">
-        <v>18.52</v>
+        <v>17.21</v>
       </c>
       <c r="P10" s="2">
-        <v>39.27</v>
+        <v>36.4</v>
       </c>
       <c r="Q10" s="2">
-        <v>4.25</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1174,45 +1177,45 @@
         <v>300</v>
       </c>
       <c r="F11">
-        <v>1938</v>
+        <v>1371</v>
       </c>
       <c r="G11">
-        <v>918</v>
+        <v>598</v>
       </c>
       <c r="H11">
-        <v>359</v>
+        <v>236</v>
       </c>
       <c r="I11">
-        <v>761</v>
+        <v>499</v>
       </c>
       <c r="J11">
-        <v>1934</v>
+        <v>1370</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="M11">
         <v>34.29</v>
       </c>
       <c r="N11">
-        <v>47.37</v>
+        <v>43.62</v>
       </c>
       <c r="O11">
-        <v>18.52</v>
+        <v>17.21</v>
       </c>
       <c r="P11">
-        <v>39.27</v>
+        <v>36.4</v>
       </c>
       <c r="Q11">
-        <v>4.25</v>
+        <v>3.01</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -1295,11 +1298,11 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2615010</v>
+      <c r="A2" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2">
         <v>1515</v>
@@ -1351,11 +1354,11 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2615010</v>
+      <c r="A3" t="s">
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>1515</v>
@@ -1407,11 +1410,11 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>2615010</v>
+      <c r="A4" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2">
         <v>1515</v>
@@ -1463,11 +1466,11 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2615010</v>
+      <c r="A5" t="s">
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1515</v>
@@ -1519,11 +1522,11 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>2615010</v>
+      <c r="A6" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2">
         <v>1515</v>
@@ -1575,11 +1578,11 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2615010</v>
+      <c r="A7" t="s">
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1515</v>
@@ -1631,11 +1634,11 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>2615030</v>
+      <c r="A8" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2">
         <v>1515</v>
@@ -1687,11 +1690,11 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2615030</v>
+      <c r="A9" t="s">
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>1515</v>
@@ -1743,11 +1746,11 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>2615030</v>
+      <c r="A10" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2">
         <v>1515</v>
@@ -1799,11 +1802,11 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>6364030</v>
+      <c r="A11" t="s">
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>6407</v>
@@ -1855,11 +1858,11 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>6364030</v>
+      <c r="A12" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2">
         <v>6407</v>
@@ -1911,11 +1914,11 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>6364040</v>
+      <c r="A13" t="s">
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>6407</v>
@@ -1967,11 +1970,11 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>6364040</v>
+      <c r="A14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2">
         <v>6407</v>
@@ -2024,7 +2027,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -2119,40 +2122,40 @@
         <v>243</v>
       </c>
       <c r="F2" s="2">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G2" s="2">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H2" s="2">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I2" s="2">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J2" s="2">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K2" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M2" s="2">
         <v>10.42</v>
       </c>
       <c r="N2" s="2">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O2" s="2">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P2" s="2">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q2" s="2">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -2172,40 +2175,40 @@
         <v>799</v>
       </c>
       <c r="F3">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G3">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H3">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I3">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J3">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M3">
         <v>34.25</v>
       </c>
       <c r="N3">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O3">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P3">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q3">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -2225,40 +2228,40 @@
         <v>575</v>
       </c>
       <c r="F4" s="2">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G4" s="2">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H4" s="2">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I4" s="2">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J4" s="2">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K4" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M4" s="2">
         <v>24.65</v>
       </c>
       <c r="N4" s="2">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O4" s="2">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P4" s="2">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q4" s="2">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -2278,40 +2281,40 @@
         <v>416</v>
       </c>
       <c r="F5">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G5">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H5">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I5">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J5">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K5">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L5">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M5">
         <v>17.83</v>
       </c>
       <c r="N5">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O5">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P5">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q5">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2331,40 +2334,40 @@
         <v>300</v>
       </c>
       <c r="F6" s="2">
-        <v>3825</v>
+        <v>1129</v>
       </c>
       <c r="G6" s="2">
-        <v>1933</v>
+        <v>591</v>
       </c>
       <c r="H6" s="2">
-        <v>674</v>
+        <v>182</v>
       </c>
       <c r="I6" s="2">
-        <v>1585</v>
+        <v>486</v>
       </c>
       <c r="J6" s="2">
-        <v>3797</v>
+        <v>1110</v>
       </c>
       <c r="K6" s="2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="M6" s="2">
         <v>12.86</v>
       </c>
       <c r="N6" s="2">
-        <v>50.54</v>
+        <v>52.35</v>
       </c>
       <c r="O6" s="2">
-        <v>17.62</v>
+        <v>16.12</v>
       </c>
       <c r="P6" s="2">
-        <v>41.44</v>
+        <v>43.05</v>
       </c>
       <c r="Q6" s="2">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -2384,40 +2387,40 @@
         <v>243</v>
       </c>
       <c r="F7">
-        <v>1887</v>
+        <v>1129</v>
       </c>
       <c r="G7">
-        <v>1015</v>
+        <v>591</v>
       </c>
       <c r="H7">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="I7">
-        <v>824</v>
+        <v>486</v>
       </c>
       <c r="J7">
-        <v>1863</v>
+        <v>1110</v>
       </c>
       <c r="K7">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L7">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M7">
         <v>16.67</v>
       </c>
       <c r="N7">
-        <v>53.79</v>
+        <v>52.35</v>
       </c>
       <c r="O7">
-        <v>16.69</v>
+        <v>16.12</v>
       </c>
       <c r="P7">
-        <v>43.67</v>
+        <v>43.05</v>
       </c>
       <c r="Q7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2437,40 +2440,40 @@
         <v>799</v>
       </c>
       <c r="F8" s="2">
-        <v>1887</v>
+        <v>1129</v>
       </c>
       <c r="G8" s="2">
-        <v>1015</v>
+        <v>591</v>
       </c>
       <c r="H8" s="2">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="I8" s="2">
-        <v>824</v>
+        <v>486</v>
       </c>
       <c r="J8" s="2">
-        <v>1863</v>
+        <v>1110</v>
       </c>
       <c r="K8" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M8" s="2">
         <v>54.8</v>
       </c>
       <c r="N8" s="2">
-        <v>53.79</v>
+        <v>52.35</v>
       </c>
       <c r="O8" s="2">
-        <v>16.69</v>
+        <v>16.12</v>
       </c>
       <c r="P8" s="2">
-        <v>43.67</v>
+        <v>43.05</v>
       </c>
       <c r="Q8" s="2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2490,40 +2493,40 @@
         <v>416</v>
       </c>
       <c r="F9">
-        <v>1887</v>
+        <v>1129</v>
       </c>
       <c r="G9">
-        <v>1015</v>
+        <v>591</v>
       </c>
       <c r="H9">
-        <v>315</v>
+        <v>182</v>
       </c>
       <c r="I9">
-        <v>824</v>
+        <v>486</v>
       </c>
       <c r="J9">
-        <v>1863</v>
+        <v>1110</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L9">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M9">
         <v>28.53</v>
       </c>
       <c r="N9">
-        <v>53.79</v>
+        <v>52.35</v>
       </c>
       <c r="O9">
-        <v>16.69</v>
+        <v>16.12</v>
       </c>
       <c r="P9">
-        <v>43.67</v>
+        <v>43.05</v>
       </c>
       <c r="Q9">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2543,40 +2546,40 @@
         <v>575</v>
       </c>
       <c r="F10" s="2">
-        <v>1938</v>
+        <v>1371</v>
       </c>
       <c r="G10" s="2">
-        <v>918</v>
+        <v>598</v>
       </c>
       <c r="H10" s="2">
-        <v>359</v>
+        <v>236</v>
       </c>
       <c r="I10" s="2">
-        <v>761</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2">
-        <v>1934</v>
+        <v>1370</v>
       </c>
       <c r="K10" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="M10" s="2">
         <v>65.71</v>
       </c>
       <c r="N10" s="2">
-        <v>47.37</v>
+        <v>43.62</v>
       </c>
       <c r="O10" s="2">
-        <v>18.52</v>
+        <v>17.21</v>
       </c>
       <c r="P10" s="2">
-        <v>39.27</v>
+        <v>36.4</v>
       </c>
       <c r="Q10" s="2">
-        <v>4.25</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2596,45 +2599,45 @@
         <v>300</v>
       </c>
       <c r="F11">
-        <v>1938</v>
+        <v>1371</v>
       </c>
       <c r="G11">
-        <v>918</v>
+        <v>598</v>
       </c>
       <c r="H11">
-        <v>359</v>
+        <v>236</v>
       </c>
       <c r="I11">
-        <v>761</v>
+        <v>499</v>
       </c>
       <c r="J11">
-        <v>1934</v>
+        <v>1370</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="M11">
         <v>34.29</v>
       </c>
       <c r="N11">
-        <v>47.37</v>
+        <v>43.62</v>
       </c>
       <c r="O11">
-        <v>18.52</v>
+        <v>17.21</v>
       </c>
       <c r="P11">
-        <v>39.27</v>
+        <v>36.4</v>
       </c>
       <c r="Q11">
-        <v>4.25</v>
+        <v>3.01</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -2717,11 +2720,11 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2615010</v>
+      <c r="A2" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2">
         <v>1515</v>
@@ -2773,11 +2776,11 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2615010</v>
+      <c r="A3" t="s">
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>1515</v>
@@ -2829,11 +2832,11 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>2615010</v>
+      <c r="A4" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2">
         <v>1515</v>
@@ -2885,11 +2888,11 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2615010</v>
+      <c r="A5" t="s">
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>1515</v>
@@ -2941,11 +2944,11 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>2615010</v>
+      <c r="A6" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2">
         <v>1515</v>
@@ -2997,11 +3000,11 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2615010</v>
+      <c r="A7" t="s">
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1515</v>
@@ -3053,11 +3056,11 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>2615030</v>
+      <c r="A8" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2">
         <v>1515</v>
@@ -3109,11 +3112,11 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2615030</v>
+      <c r="A9" t="s">
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>1515</v>
@@ -3165,11 +3168,11 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>2615030</v>
+      <c r="A10" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2">
         <v>1515</v>
@@ -3221,11 +3224,11 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>6364030</v>
+      <c r="A11" t="s">
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>6407</v>
@@ -3277,11 +3280,11 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>6364030</v>
+      <c r="A12" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2">
         <v>6407</v>
@@ -3333,11 +3336,11 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>6364040</v>
+      <c r="A13" t="s">
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>6407</v>
@@ -3389,11 +3392,11 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>6364040</v>
+      <c r="A14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2">
         <v>6407</v>
@@ -3446,7 +3449,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -3461,98 +3464,98 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
